--- a/backtest_runs/20260410_193731/by_symbol/IBLHL/IBLHL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/IBLHL/IBLHL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -633,7 +633,7 @@
         <v>-5543.020000000006</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="3" t="n">
         <v>103656.53</v>
@@ -679,7 +679,7 @@
         <v>-7289.770000000006</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>96366.75999999999</v>
@@ -863,7 +863,7 @@
         <v>-1653.590000000002</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>105473.15</v>
@@ -909,7 +909,7 @@
         <v>-2561.900000000003</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>102911.25</v>
@@ -1047,7 +1047,7 @@
         <v>-209.6100000000079</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>109432.45</v>
@@ -1185,7 +1185,7 @@
         <v>-3936.010000000011</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>108524.14</v>
@@ -1231,7 +1231,7 @@
         <v>-3726.399999999987</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="3" t="n">
         <v>104797.74</v>
@@ -1277,7 +1277,7 @@
         <v>-6870.550000000007</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>97927.19</v>
@@ -1415,7 +1415,7 @@
         <v>-1607.010000000011</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>102934.54</v>
@@ -1461,7 +1461,7 @@
         <v>-745.2800000000007</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>102189.26</v>
